--- a/fixtures/sml/filtering/auto-filter.xlsx
+++ b/fixtures/sml/filtering/auto-filter.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Value</t>
+    <t>Category</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Category</t>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -29,10 +29,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
